--- a/output/pdf_financials_xlsx/SAI.H.xlsx
+++ b/output/pdf_financials_xlsx/SAI.H.xlsx
@@ -2163,40 +2163,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.412581</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.090072</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.036212</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.083588</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.044681</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002735</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.049413</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.011453</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001934</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.006394</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003499</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004807</v>
       </c>
     </row>
     <row r="35">
@@ -2249,40 +2249,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.412581</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.090072</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.036212</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.083588</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.044681</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002735</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.049413</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.011453</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.001934</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.006394</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003499</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004807</v>
       </c>
     </row>
     <row r="37">
@@ -2765,40 +2765,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.544242</v>
+        <v>0.131661</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.241835</v>
+        <v>0.151763</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.203152</v>
+        <v>0.16694</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.235394</v>
+        <v>0.151806</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.819068</v>
+        <v>2.774387</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.113283</v>
+        <v>0.110548</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.057833</v>
+        <v>0.00842</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.016295</v>
+        <v>0.004842</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.011236</v>
+        <v>0.004842</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.008340999999999999</v>
+        <v>0.004842</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.009649</v>
+        <v>0.004842</v>
       </c>
     </row>
     <row r="49">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -20274,7 +20274,11 @@
           <t>General and administrative expenses 15/19</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -23342,7 +23346,11 @@
           <t>General and administrative expenses 16/20</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SAI.H.xlsx
+++ b/output/pdf_financials_xlsx/SAI.H.xlsx
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.338614</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.218529</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.955736</v>
+        <v>-0.6171219999999999</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.994702</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-14.81865775027541</v>
+        <v>-9.568457929978006</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-18.66779720435895</v>
@@ -5103,22 +5103,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.338614</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.397104</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.366714</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.33513</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.282583</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.042415</v>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
@@ -15120,7 +15120,11 @@
           <t>Depreciation of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19012,7 +19016,11 @@
           <t>Depreciation of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
         <v>0.338614</v>
       </c>
